--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-100_p-20_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-100_p-20_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.18113478490298</v>
+        <v>73.83498127146429</v>
       </c>
       <c r="C2" t="n">
-        <v>78.94527996271543</v>
+        <v>73.3325829835305</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6703862973488868</v>
+        <v>0.7404277667403221</v>
       </c>
       <c r="E2" t="n">
-        <v>79.18113478490298</v>
+        <v>73.83498127146429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.70220330625698</v>
+        <v>79.41418178357944</v>
       </c>
       <c r="C3" t="n">
-        <v>84.55164453419326</v>
+        <v>79.51433239293603</v>
       </c>
       <c r="D3" t="n">
-        <v>0.445610912827154</v>
+        <v>0.5719492215663194</v>
       </c>
       <c r="E3" t="n">
-        <v>84.70220330625696</v>
+        <v>79.41418178357944</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86.69858735802214</v>
+        <v>77.13881607972387</v>
       </c>
       <c r="C4" t="n">
-        <v>86.44422986528812</v>
+        <v>76.96931535289346</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3609826916518311</v>
+        <v>0.5838485334068537</v>
       </c>
       <c r="E4" t="n">
-        <v>86.69858735802214</v>
+        <v>77.13881607972387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.82907291585568</v>
+        <v>79.21495860690837</v>
       </c>
       <c r="C5" t="n">
-        <v>79.96726653779949</v>
+        <v>79.09030577108231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4899869673264523</v>
+        <v>0.559760915239652</v>
       </c>
       <c r="E5" t="n">
-        <v>80.82907291585568</v>
+        <v>79.21495860690837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.94270711684358</v>
+        <v>76.6638119706918</v>
       </c>
       <c r="C6" t="n">
-        <v>76.88350248246522</v>
+        <v>76.46278448190048</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5927428235610326</v>
+        <v>0.683163724342982</v>
       </c>
       <c r="E6" t="n">
-        <v>76.94270711684358</v>
+        <v>76.6638119706918</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.70327597989602</v>
+        <v>78.38034931098019</v>
       </c>
       <c r="C7" t="n">
-        <v>78.75844755879767</v>
+        <v>78.03040148911283</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5570470968882243</v>
+        <v>0.5404553378621737</v>
       </c>
       <c r="E7" t="n">
-        <v>78.70327597989601</v>
+        <v>78.38034931098021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.68869107864255</v>
+        <v>73.64060242735664</v>
       </c>
       <c r="C8" t="n">
-        <v>82.36803554281902</v>
+        <v>73.60537388545795</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4067066107624365</v>
+        <v>0.6821377820024888</v>
       </c>
       <c r="E8" t="n">
-        <v>82.68869107864255</v>
+        <v>73.64060242735664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.55419164525645</v>
+        <v>79.65380323359199</v>
       </c>
       <c r="C9" t="n">
-        <v>84.28597428971602</v>
+        <v>78.28214447430331</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4066940041258931</v>
+        <v>0.5891763059732814</v>
       </c>
       <c r="E9" t="n">
-        <v>84.55419164525645</v>
+        <v>79.65380323359199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87.71053382814731</v>
+        <v>83.83653837835968</v>
       </c>
       <c r="C10" t="n">
-        <v>87.42837411353955</v>
+        <v>83.61361505066046</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3003667497231314</v>
+        <v>0.4283985489048064</v>
       </c>
       <c r="E10" t="n">
-        <v>87.71053382814731</v>
+        <v>83.83653837835968</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82.43323904186022</v>
+        <v>77.25715620377339</v>
       </c>
       <c r="C11" t="n">
-        <v>82.33375714675159</v>
+        <v>76.85073368446054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.476185465650633</v>
+        <v>0.7309750054962934</v>
       </c>
       <c r="E11" t="n">
-        <v>82.43323904186022</v>
+        <v>77.25715620377339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80.33469147656987</v>
+        <v>71.12250105969775</v>
       </c>
       <c r="C12" t="n">
-        <v>79.6690994072288</v>
+        <v>70.76981682777367</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5927751675830223</v>
+        <v>0.7423800770193338</v>
       </c>
       <c r="E12" t="n">
-        <v>80.33469147656987</v>
+        <v>71.12250105969774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87.76053426067699</v>
+        <v>64.91223972525714</v>
       </c>
       <c r="C13" t="n">
-        <v>86.811399347427</v>
+        <v>63.4896149753768</v>
       </c>
       <c r="D13" t="n">
-        <v>0.406819339573849</v>
+        <v>1.248579393823942</v>
       </c>
       <c r="E13" t="n">
-        <v>87.76053426067699</v>
+        <v>64.91223972525714</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.70552513430047</v>
+        <v>70.29489874479883</v>
       </c>
       <c r="C14" t="n">
-        <v>78.40938367020136</v>
+        <v>69.05906059329661</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5298749527583519</v>
+        <v>0.7772609094778697</v>
       </c>
       <c r="E14" t="n">
-        <v>78.70552513430047</v>
+        <v>70.29489874479883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83.39250339535809</v>
+        <v>76.84971323281343</v>
       </c>
       <c r="C15" t="n">
-        <v>83.38562250059826</v>
+        <v>76.71569477726743</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4313007143403714</v>
+        <v>0.684617818260449</v>
       </c>
       <c r="E15" t="n">
-        <v>83.39250339535809</v>
+        <v>76.84971323281343</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77.02289812195608</v>
+        <v>66.58474554278152</v>
       </c>
       <c r="C16" t="n">
-        <v>76.7141715417284</v>
+        <v>66.2546192951261</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6167609031777829</v>
+        <v>1.099992229789496</v>
       </c>
       <c r="E16" t="n">
-        <v>77.02289812195606</v>
+        <v>66.58474554278152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.98264690871028</v>
+        <v>75.25328650478522</v>
       </c>
       <c r="C17" t="n">
-        <v>83.82246686527176</v>
+        <v>74.80269306901189</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4468096090558295</v>
+        <v>0.7108749046604176</v>
       </c>
       <c r="E17" t="n">
-        <v>83.98264690871028</v>
+        <v>75.25328650478522</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.33956176091489</v>
+        <v>5.008487738818204</v>
       </c>
       <c r="C18" t="n">
-        <v>83.18463869561245</v>
+        <v>5.227796872452148</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4559462277412726</v>
+        <v>0.2051692620545518</v>
       </c>
       <c r="E18" t="n">
-        <v>83.33956176091489</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>86.96286300054498</v>
-      </c>
-      <c r="C19" t="n">
-        <v>86.98624672263411</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3824953511667749</v>
-      </c>
-      <c r="E19" t="n">
-        <v>86.96286300054498</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>77.06243133591121</v>
-      </c>
-      <c r="C20" t="n">
-        <v>76.58601529036191</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5965195772548516</v>
-      </c>
-      <c r="E20" t="n">
-        <v>77.06243133591121</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>75.10722411093522</v>
-      </c>
-      <c r="C21" t="n">
-        <v>74.79212230522646</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.6724087037922193</v>
-      </c>
-      <c r="E21" t="n">
-        <v>75.10722411093522</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>83.66266144170797</v>
-      </c>
-      <c r="C22" t="n">
-        <v>83.33107119293825</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.4967615285577874</v>
-      </c>
-      <c r="E22" t="n">
-        <v>83.66266144170797</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>77.53458074896841</v>
-      </c>
-      <c r="C23" t="n">
-        <v>76.77450938735606</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6095192831009626</v>
-      </c>
-      <c r="E23" t="n">
-        <v>77.53458074896841</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>84.16050311853908</v>
-      </c>
-      <c r="C24" t="n">
-        <v>84.11066469059085</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4203381919767707</v>
-      </c>
-      <c r="E24" t="n">
-        <v>84.16050311853908</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>82.00935994256005</v>
-      </c>
-      <c r="C25" t="n">
-        <v>81.85115048887108</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4688383126631379</v>
-      </c>
-      <c r="E25" t="n">
-        <v>82.00935994256005</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>79.7639252934714</v>
-      </c>
-      <c r="C26" t="n">
-        <v>79.42376815756317</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.5423570035335918</v>
-      </c>
-      <c r="E26" t="n">
-        <v>79.7639252934714</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>72.65815448230521</v>
-      </c>
-      <c r="C27" t="n">
-        <v>71.91806233642876</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7719376289751381</v>
-      </c>
-      <c r="E27" t="n">
-        <v>72.65815448230521</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>78.73658076626961</v>
-      </c>
-      <c r="C28" t="n">
-        <v>78.46375558183655</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6345109183341264</v>
-      </c>
-      <c r="E28" t="n">
-        <v>78.73658076626961</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>88.14661026479469</v>
-      </c>
-      <c r="C29" t="n">
-        <v>88.07556945422114</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3724575954799851</v>
-      </c>
-      <c r="E29" t="n">
-        <v>88.14661026479467</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>90.209603889307</v>
-      </c>
-      <c r="C30" t="n">
-        <v>90.29829152738481</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2745036771520972</v>
-      </c>
-      <c r="E30" t="n">
-        <v>90.209603889307</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>90.76955683007638</v>
-      </c>
-      <c r="C31" t="n">
-        <v>90.21590864560338</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.2834494753818338</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.76955683007638</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>82.19220177798539</v>
-      </c>
-      <c r="C32" t="n">
-        <v>81.89301432810568</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4904364593821811</v>
-      </c>
-      <c r="E32" t="n">
-        <v>82.19220177798539</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4.479473222487619</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4.549038787172921</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1210619779750505</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4.479473222487618</v>
+        <v>5.008487738818205</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.19220177798539</v>
+        <v>75.25328650478522</v>
       </c>
       <c r="B2" t="n">
-        <v>81.89301432810568</v>
+        <v>74.80269306901189</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4904364593821811</v>
+        <v>0.7108749046604176</v>
       </c>
       <c r="D2" t="n">
-        <v>82.19220177798539</v>
+        <v>75.25328650478522</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4.479473222487619</v>
+        <v>5.008487738818204</v>
       </c>
       <c r="B3" t="n">
-        <v>4.549038787172921</v>
+        <v>5.227796872452148</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1210619779750505</v>
+        <v>0.2051692620545518</v>
       </c>
       <c r="D3" t="n">
-        <v>4.479473222487618</v>
+        <v>5.008487738818205</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.19220177798539</v>
+        <v>75.25328650478522</v>
       </c>
       <c r="B2" t="n">
-        <v>4.479473222487619</v>
+        <v>5.008487738818204</v>
       </c>
       <c r="C2" t="n">
-        <v>81.89301432810568</v>
+        <v>74.80269306901189</v>
       </c>
       <c r="D2" t="n">
-        <v>4.549038787172921</v>
+        <v>5.227796872452148</v>
       </c>
       <c r="E2" t="n">
-        <v>82.19220177798539</v>
+        <v>75.25328650478522</v>
       </c>
       <c r="F2" t="n">
-        <v>4.479473222487618</v>
+        <v>5.008487738818205</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4904364593821811</v>
+        <v>0.7108749046604176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1210619779750505</v>
+        <v>0.2051692620545518</v>
       </c>
     </row>
   </sheetData>
